--- a/水库项目出表/Template/权属情况汇总表.xlsx
+++ b/水库项目出表/Template/权属情况汇总表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sunchuanhong\Local\code\水库项目出表\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="825" yWindow="3645" windowWidth="21555" windowHeight="9630"/>
+    <workbookView xWindow="830" yWindow="3650" windowWidth="21560" windowHeight="9630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +32,6 @@
     <t>土地所在地  : #区县名#</t>
   </si>
   <si>
-    <t>单位：公顷</t>
-  </si>
-  <si>
     <t>序  号</t>
   </si>
   <si>
@@ -67,13 +69,17 @@
   </si>
   <si>
     <t xml:space="preserve">注：土地登记状况栏，没有进行土地登记发证的，由土地权利人签名盖章认可，表格下方加盖县（市、区）土地行政主管部门章确认  </t>
+  </si>
+  <si>
+    <t>单位：#单位#</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,11 +202,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -242,7 +256,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -274,9 +288,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,6 +323,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -483,18 +499,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
-    <col min="4" max="4" width="24.25" customWidth="1"/>
-    <col min="5" max="8" width="13.375" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" customWidth="1"/>
+    <col min="5" max="8" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.95" customHeight="1">
+    <row r="1" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -506,7 +522,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -519,34 +535,34 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -554,51 +570,51 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -631,9 +647,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -641,9 +657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
